--- a/diccionarioDatosDelivery.xlsx
+++ b/diccionarioDatosDelivery.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Diccionario de Datos Corregido " sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Diccionario de Datos Estructura" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,21 +11,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="177">
   <si>
     <t>Tabla</t>
   </si>
   <si>
-    <t>Atributo</t>
-  </si>
-  <si>
-    <t>Tipo de Dato</t>
-  </si>
-  <si>
-    <t>Clave</t>
-  </si>
-  <si>
-    <t>Nulidad</t>
+    <t>Columna</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>Referencia</t>
+  </si>
+  <si>
+    <t>NOT NULL</t>
   </si>
   <si>
     <t>Descripción</t>
@@ -37,91 +43,232 @@
     <t>id_suscripcion</t>
   </si>
   <si>
+    <t>SERIAL</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Identificador único autoincremental de la suscripción [cite: 57].</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>Nombre o categoría del plan (ej. Premium) [cite: 57].</t>
+  </si>
+  <si>
+    <t>costo_mensual</t>
+  </si>
+  <si>
+    <t>DECIMAL(10,2)</t>
+  </si>
+  <si>
+    <t>Precio mensual de la suscripción [cite: 57].</t>
+  </si>
+  <si>
+    <t>descuento_envio</t>
+  </si>
+  <si>
+    <t>DECIMAL(5,2)</t>
+  </si>
+  <si>
+    <t>Porcentaje de descuento aplicado a los envíos [cite: 57].</t>
+  </si>
+  <si>
+    <t>REPARTIDOR</t>
+  </si>
+  <si>
+    <t>id_repartidor</t>
+  </si>
+  <si>
+    <t>Identificador único del repartidor [cite: 65].</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>Nombre completo del repartidor [cite: 65].</t>
+  </si>
+  <si>
+    <t>vehiculo</t>
+  </si>
+  <si>
+    <t>Tipo de transporte (bicicleta, moto, auto) [cite:20, 65]</t>
+  </si>
+  <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>Número de contacto del repartidor [cite: 65].</t>
+  </si>
+  <si>
+    <t>calificacion_promedio</t>
+  </si>
+  <si>
+    <t>DECIMAL(3,2)</t>
+  </si>
+  <si>
+    <t>Promedio de notas recibidas por clientes [cite: 65].</t>
+  </si>
+  <si>
+    <t>CUPON</t>
+  </si>
+  <si>
+    <t>id_cupon</t>
+  </si>
+  <si>
+    <t>Identificador único del cupón [cite: 66].</t>
+  </si>
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>Código alfanumérico único para aplicar el descuento [cite: 66].</t>
+  </si>
+  <si>
+    <t>porcentaje</t>
+  </si>
+  <si>
+    <t>Porcentaje de rebaja sobre el pedido [cite: 66].</t>
+  </si>
+  <si>
+    <t>fecha_expira</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Fecha límite de validez del cupón [cite: 66].</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>Estado actual del cupón (ej. Activo/Inactivo) [cite: 66].</t>
+  </si>
+  <si>
+    <t>COMERCIO</t>
+  </si>
+  <si>
+    <t>id_comercio</t>
+  </si>
+  <si>
+    <t>Identificador único del comercio [cite: 60].</t>
+  </si>
+  <si>
+    <t>Nombre del establecimiento comercial [cite: 60].</t>
+  </si>
+  <si>
+    <t>rubro</t>
+  </si>
+  <si>
+    <t>Categoría del negocio (ej. Comida Rápida) [cite: 60].</t>
+  </si>
+  <si>
+    <t>direccion</t>
+  </si>
+  <si>
+    <t>VARCHAR(200)</t>
+  </si>
+  <si>
+    <t>Dirección física del comercio [cite: 60].</t>
+  </si>
+  <si>
+    <t>latitud</t>
+  </si>
+  <si>
+    <t>DECIMAL(10,8)</t>
+  </si>
+  <si>
+    <t>Coordenada de latitud para GPS [cite: 60].</t>
+  </si>
+  <si>
+    <t>longitud</t>
+  </si>
+  <si>
+    <t>DECIMAL(11,8)</t>
+  </si>
+  <si>
+    <t>Coordenada de longitud para GPS [cite: 60].</t>
+  </si>
+  <si>
+    <t>CLIENTE</t>
+  </si>
+  <si>
+    <t>id_cliente</t>
+  </si>
+  <si>
+    <t>Identificador único del cliente [cite: 58].</t>
+  </si>
+  <si>
+    <t>Nombre completo del usuario [cite: 58].</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Correo electrónico único de registro [cite: 58].</t>
+  </si>
+  <si>
+    <t>Teléfono de contacto del cliente [cite: 58].</t>
+  </si>
+  <si>
     <t>INT</t>
   </si>
   <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>No Nulo</t>
-  </si>
-  <si>
-    <t>Identificador único del plan de suscripción.</t>
-  </si>
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>VARCHAR(50)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Nombre del plan (ej. Prime o Gold).</t>
-  </si>
-  <si>
-    <t>costo_mensual</t>
-  </si>
-  <si>
-    <t>DECIMAL(10,2)</t>
-  </si>
-  <si>
-    <t>Precio mensual del plan.</t>
-  </si>
-  <si>
-    <t>descuento_envio</t>
-  </si>
-  <si>
-    <t>DECIMAL(5,2)</t>
-  </si>
-  <si>
-    <t>Porcentaje de descuento aplicado a envíos.</t>
-  </si>
-  <si>
-    <t>CLIENTE</t>
-  </si>
-  <si>
-    <t>id_cliente</t>
-  </si>
-  <si>
-    <t>Identificador único del cliente.</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>VARCHAR(100)</t>
-  </si>
-  <si>
-    <t>Nombre completo del usuario.</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>VARCHAR(255)</t>
-  </si>
-  <si>
-    <t>Correo electrónico único.</t>
-  </si>
-  <si>
-    <t>telefono</t>
-  </si>
-  <si>
-    <t>VARCHAR(20)</t>
-  </si>
-  <si>
-    <t>Nulo</t>
-  </si>
-  <si>
-    <t>Número de contacto.</t>
-  </si>
-  <si>
-    <t>FK</t>
-  </si>
-  <si>
-    <t>Relación con el plan de suscripción.</t>
+    <t>SUSCRIPCION(id_suscripcion)</t>
+  </si>
+  <si>
+    <t>Referencia al plan de suscripción contratado [cite: 58].</t>
+  </si>
+  <si>
+    <t>PRODUCTO</t>
+  </si>
+  <si>
+    <t>id_producto</t>
+  </si>
+  <si>
+    <t>Identificador único del producto [cite: 61].</t>
+  </si>
+  <si>
+    <t>Nombre comercial del producto [cite: 61].</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>Detalle o ingredientes del producto [cite: 61].</t>
+  </si>
+  <si>
+    <t>precio</t>
+  </si>
+  <si>
+    <t>Valor unitario del producto [cite: 61].</t>
+  </si>
+  <si>
+    <t>COMERCIO(id_comercio)</t>
+  </si>
+  <si>
+    <t>Referencia al comercio que ofrece el producto [cite: 61].</t>
   </si>
   <si>
     <t>DIRECCION</t>
@@ -130,16 +277,13 @@
     <t>id_direccion</t>
   </si>
   <si>
-    <t>Identificador único de la dirección.</t>
-  </si>
-  <si>
-    <t>Cliente propietario de la dirección.</t>
-  </si>
-  <si>
-    <t>etiqueta</t>
-  </si>
-  <si>
-    <t>Nombre (ej. Casa o Trabajo).</t>
+    <t>Identificador único de la dirección [cite: 59].</t>
+  </si>
+  <si>
+    <t>CLIENTE(id_cliente)</t>
+  </si>
+  <si>
+    <t>Referencia al cliente dueño de la dirección [cite: 59].</t>
   </si>
   <si>
     <t>calle</t>
@@ -148,85 +292,19 @@
     <t>VARCHAR(150)</t>
   </si>
   <si>
-    <t>Nombre de la vía pública.</t>
+    <t>Nombre de la vía o calle [cite: 59].</t>
   </si>
   <si>
     <t>numero</t>
   </si>
   <si>
-    <t>VARCHAR(10)</t>
-  </si>
-  <si>
-    <t>Numeración domiciliaria.</t>
-  </si>
-  <si>
-    <t>latitud</t>
-  </si>
-  <si>
-    <t>DECIMAL(9,6)</t>
-  </si>
-  <si>
-    <t>Coordenada geográfica para GPS.</t>
-  </si>
-  <si>
-    <t>longitud</t>
-  </si>
-  <si>
-    <t>COMERCIO</t>
-  </si>
-  <si>
-    <t>id_comercio</t>
-  </si>
-  <si>
-    <t>ID único del establecimiento.</t>
-  </si>
-  <si>
-    <t>Nombre comercial del local.</t>
-  </si>
-  <si>
-    <t>rubro</t>
-  </si>
-  <si>
-    <t>Categoría (ej. Restaurante o Farmacia).</t>
-  </si>
-  <si>
-    <t>direccion</t>
-  </si>
-  <si>
-    <t>Dirección física del comercio.</t>
-  </si>
-  <si>
-    <t>Ubicación geográfica del local.</t>
-  </si>
-  <si>
-    <t>PRODUCTO</t>
-  </si>
-  <si>
-    <t>id_producto</t>
-  </si>
-  <si>
-    <t>ID único del producto.</t>
-  </si>
-  <si>
-    <t>Nombre comercial del producto.</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-  </si>
-  <si>
-    <t>Detalle de ingredientes o características.</t>
-  </si>
-  <si>
-    <t>precio</t>
-  </si>
-  <si>
-    <t>Precio unitario de venta.</t>
-  </si>
-  <si>
-    <t>Establecimiento al que pertenece.</t>
+    <t>Numeración domiciliaria [cite: 59].</t>
+  </si>
+  <si>
+    <t>Ubicación geográfica (latitud) [cite: 59].</t>
+  </si>
+  <si>
+    <t>Ubicación geográfica (longitud) [cite: 59].</t>
   </si>
   <si>
     <t>COMPLEMENTO</t>
@@ -235,19 +313,22 @@
     <t>id_complemento</t>
   </si>
   <si>
-    <t>ID único del extra o adición.</t>
-  </si>
-  <si>
-    <t>Producto al que se asocia.</t>
-  </si>
-  <si>
-    <t>Nombre del extra (ej. Queso extra).</t>
+    <t>ID único del complemento o extra [cite: 62].</t>
+  </si>
+  <si>
+    <t>PRODUCTO(id_producto)</t>
+  </si>
+  <si>
+    <t>Referencia al producto al que se asocia [cite: 62].</t>
+  </si>
+  <si>
+    <t>Nombre del extra (ej. Queso extra) [cite: 62].</t>
   </si>
   <si>
     <t>precio_extra</t>
   </si>
   <si>
-    <t>Costo adicional del complemento.</t>
+    <t>Costo adicional por el complemento [cite: 62].</t>
   </si>
   <si>
     <t>CARRITO</t>
@@ -256,19 +337,19 @@
     <t>id_carrito</t>
   </si>
   <si>
-    <t>ID de la sesión de compra.</t>
-  </si>
-  <si>
-    <t>Dueño del carrito.</t>
+    <t>Identificador del carrito de compra [cite: 63].</t>
+  </si>
+  <si>
+    <t>Referencia al cliente propietario del carrito [cite: 63].</t>
   </si>
   <si>
     <t>fecha_creacion</t>
   </si>
   <si>
-    <t>DATETIME</t>
-  </si>
-  <si>
-    <t>Momento en que se inició la compra.</t>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Fecha y hora de inicio de la sesión de compra [cite: 63].</t>
   </si>
   <si>
     <t>ITEM_CARRITO</t>
@@ -277,88 +358,22 @@
     <t>id_item</t>
   </si>
   <si>
-    <t>ID único de la línea de producto.</t>
-  </si>
-  <si>
-    <t>Carrito al que pertenece el ítem.</t>
-  </si>
-  <si>
-    <t>Producto seleccionado.</t>
+    <t>ID de la línea de producto en el carrito [cite: 64].</t>
+  </si>
+  <si>
+    <t>CARRITO(id_carrito)</t>
+  </si>
+  <si>
+    <t>Referencia al carrito principal [cite: 64].</t>
+  </si>
+  <si>
+    <t>Referencia al producto seleccionado [cite: 64].</t>
   </si>
   <si>
     <t>cantidad</t>
   </si>
   <si>
-    <t>Unidades seleccionadas.</t>
-  </si>
-  <si>
-    <t>REPARTIDOR</t>
-  </si>
-  <si>
-    <t>id_repartidor</t>
-  </si>
-  <si>
-    <t>ID único del agente móvil.</t>
-  </si>
-  <si>
-    <t>Nombre del transportista.</t>
-  </si>
-  <si>
-    <t>vehiculo</t>
-  </si>
-  <si>
-    <t>Tipo (Bicicleta o Moto).</t>
-  </si>
-  <si>
-    <t>Contacto del repartidor.</t>
-  </si>
-  <si>
-    <t>calificacion_promedio</t>
-  </si>
-  <si>
-    <t>DECIMAL(3,2)</t>
-  </si>
-  <si>
-    <t>Media de valoraciones de clientes.</t>
-  </si>
-  <si>
-    <t>CUPON</t>
-  </si>
-  <si>
-    <t>id_cupon</t>
-  </si>
-  <si>
-    <t>ID único del descuento.</t>
-  </si>
-  <si>
-    <t>codigo</t>
-  </si>
-  <si>
-    <t>Código alfanumérico para aplicar.</t>
-  </si>
-  <si>
-    <t>pct_descuento</t>
-  </si>
-  <si>
-    <t>Porcentaje de rebaja.</t>
-  </si>
-  <si>
-    <t>fecha_expira</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>Vencimiento del beneficio.</t>
-  </si>
-  <si>
-    <t>activo</t>
-  </si>
-  <si>
-    <t>BOOLEAN</t>
-  </si>
-  <si>
-    <t>Estado de vigencia del cupón.</t>
+    <t>Unidades del producto en el carrito [cite: 64].</t>
   </si>
   <si>
     <t>PEDIDO</t>
@@ -367,46 +382,79 @@
     <t>id_pedido</t>
   </si>
   <si>
-    <t>Folio transaccional único.</t>
+    <t>Identificador único del pedido finalizado [cite: 67].</t>
   </si>
   <si>
     <t>fecha</t>
   </si>
   <si>
-    <t>Fecha y hora del pedido.</t>
+    <t>Fecha y hora de generación del pedido [cite: 67].</t>
   </si>
   <si>
     <t>total_productos</t>
   </si>
   <si>
-    <t>DECIMAL(12,2)</t>
-  </si>
-  <si>
-    <t>Suma total de los ítems.</t>
+    <t>Suma total de precios de productos [cite: 67].</t>
   </si>
   <si>
     <t>costo_envio</t>
   </si>
   <si>
-    <t>Tarifa según fórmula D x K x F.</t>
+    <t>Cargo por transporte y logística [cite: 39, 67]</t>
   </si>
   <si>
     <t>distancia_km</t>
   </si>
   <si>
-    <t>Km entre comercio y entrega.</t>
-  </si>
-  <si>
-    <t>Cliente que realizó el pedido.</t>
-  </si>
-  <si>
-    <t>Comercio que prepara el pedido.</t>
-  </si>
-  <si>
-    <t>Repartidor asignado.</t>
-  </si>
-  <si>
-    <t>Cupón aplicado al pedido.</t>
+    <t>DECIMAL(6,2)</t>
+  </si>
+  <si>
+    <t>Distancia recorrida para la entrega [cite: 67].</t>
+  </si>
+  <si>
+    <t>Cliente que realiza la compra [cite: 67].</t>
+  </si>
+  <si>
+    <t>Comercio donde se realiza la compra [cite: 67].</t>
+  </si>
+  <si>
+    <t>REPARTIDOR(id_repartidor)</t>
+  </si>
+  <si>
+    <t>Repartidor asignado al traslado [cite: 67].</t>
+  </si>
+  <si>
+    <t>CUPON(id_cupon)</t>
+  </si>
+  <si>
+    <t>Cupón de descuento aplicado [cite: 67].</t>
+  </si>
+  <si>
+    <t>DETALLE_PEDIDO</t>
+  </si>
+  <si>
+    <t>id_detalle</t>
+  </si>
+  <si>
+    <t>ID del desglose individual de cada producto pedido.</t>
+  </si>
+  <si>
+    <t>PEDIDO(id_pedido)</t>
+  </si>
+  <si>
+    <t>Referencia al pedido padre.</t>
+  </si>
+  <si>
+    <t>Producto incluido en el pedido.</t>
+  </si>
+  <si>
+    <t>Cantidad comprada de ese producto.</t>
+  </si>
+  <si>
+    <t>precio_unitario</t>
+  </si>
+  <si>
+    <t>Precio del producto en el momento del pedido.</t>
   </si>
   <si>
     <t>PAGO</t>
@@ -415,136 +463,85 @@
     <t>id_pago</t>
   </si>
   <si>
-    <t>ID único de la transacción.</t>
-  </si>
-  <si>
-    <t>Pedido asociado al pago.</t>
+    <t>Identificador único de la transacción [cite: 68].</t>
+  </si>
+  <si>
+    <t>Referencia al pedido pagado [cite: 68].</t>
   </si>
   <si>
     <t>metodo_pago</t>
   </si>
   <si>
-    <t>Ej. Tarjeta de crédito o Débito.</t>
+    <t>Medio de pago utilizado (ej. Débito) [cite: 68].</t>
   </si>
   <si>
     <t>monto_final</t>
   </si>
   <si>
-    <t>Total pagado por el cliente.</t>
-  </si>
-  <si>
-    <t>estado</t>
-  </si>
-  <si>
-    <t>Estado (Aprobado o Pendiente).</t>
+    <t>Total pagado tras descuentos [cite: 68].</t>
+  </si>
+  <si>
+    <t>Estado de la transacción (ej. Aprobado) [cite: 68].</t>
   </si>
   <si>
     <t>fecha_pago</t>
   </si>
   <si>
-    <t>Confirmación de la pasarela.</t>
+    <t>Fecha y hora de confirmación del pago [cite: 68].</t>
+  </si>
+  <si>
+    <t>RECLAMO</t>
+  </si>
+  <si>
+    <t>id_reclamo</t>
+  </si>
+  <si>
+    <t>Identificador único del reclamo.</t>
+  </si>
+  <si>
+    <t>Referencia al pedido con la incidencia.</t>
+  </si>
+  <si>
+    <t>Detalle del inconveniente reportado.</t>
+  </si>
+  <si>
+    <t>Fase de resolución del reclamo.</t>
   </si>
   <si>
     <t>VALORACION_PEDIDO</t>
   </si>
   <si>
-    <t>id_val_pedido</t>
-  </si>
-  <si>
-    <t>ID de valoración general.</t>
-  </si>
-  <si>
-    <t>Pedido evaluado.</t>
+    <t>id_valoracion</t>
+  </si>
+  <si>
+    <t>Identificador único de la calificación [cite: 70].</t>
+  </si>
+  <si>
+    <t>Referencia al pedido evaluado [cite: 70].</t>
   </si>
   <si>
     <t>nota_comercio</t>
   </si>
   <si>
-    <t>Calificación del local (1-5).</t>
+    <t>Calificación al local (1-5) [cite: 60, 70]</t>
   </si>
   <si>
     <t>nota_repartidor</t>
   </si>
   <si>
-    <t>Calificación del repartidor (1-5).</t>
-  </si>
-  <si>
-    <t>comentario_general</t>
-  </si>
-  <si>
-    <t>Feedback adicional del cliente.</t>
+    <t>Calificación al repartidor (1-5) [cite: 60, 70]</t>
+  </si>
+  <si>
+    <t>comentario</t>
+  </si>
+  <si>
+    <t>Opinión escrita del cliente [cite: 70].</t>
   </si>
   <si>
     <t>fecha_valoracion</t>
   </si>
   <si>
-    <t>Fecha de la calificación.</t>
-  </si>
-  <si>
-    <t>VALORACION_PRODUCTO</t>
-  </si>
-  <si>
-    <t>id_val_prod</t>
-  </si>
-  <si>
-    <t>ID de valoración del plato.</t>
-  </si>
-  <si>
-    <t>Pedido fuente.</t>
-  </si>
-  <si>
-    <t>Producto específico evaluado.</t>
-  </si>
-  <si>
-    <t>nota</t>
-  </si>
-  <si>
-    <t>Calificación del producto (1-5).</t>
-  </si>
-  <si>
-    <t>comentario</t>
-  </si>
-  <si>
-    <t>Opinión sobre el plato.</t>
-  </si>
-  <si>
-    <t>MOTIVO_RECLAMO</t>
-  </si>
-  <si>
-    <t>id_motivo</t>
-  </si>
-  <si>
-    <t>ID de categoría de queja.</t>
-  </si>
-  <si>
-    <t>Ej. Comida fría o Pedido incompleto.</t>
-  </si>
-  <si>
-    <t>RECLAMO</t>
-  </si>
-  <si>
-    <t>id_reclamo</t>
-  </si>
-  <si>
-    <t>ID único del reclamo.</t>
-  </si>
-  <si>
-    <t>Pedido con incidencias.</t>
-  </si>
-  <si>
-    <t>Tipo de incidencia.</t>
-  </si>
-  <si>
-    <t>descripcion_detalle</t>
-  </si>
-  <si>
-    <t>Explicación del usuario.</t>
-  </si>
-  <si>
-    <t>estado_resolucion</t>
-  </si>
-  <si>
-    <t>Estado (Abierto o Resuelto).</t>
+    <t>Fecha de registro de la reseña [cite: 70].</t>
   </si>
 </sst>
 </file>
@@ -801,6 +798,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.25"/>
+    <col customWidth="1" min="6" max="6" width="20.88"/>
+    <col customWidth="1" min="8" max="8" width="47.5"/>
+    <col customWidth="1" min="9" max="9" width="12.0"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -821,685 +824,895 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>36</v>
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>65</v>
+        <v>13</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>70</v>
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>74</v>
+        <v>13</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>75</v>
+        <v>13</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>78</v>
+        <v>13</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>82</v>
+        <v>13</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>85</v>
+        <v>13</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="36">
@@ -1507,19 +1720,25 @@
         <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>88</v>
+        <v>13</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37">
@@ -1527,779 +1746,1014 @@
         <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>89</v>
+        <v>13</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>90</v>
+        <v>13</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>95</v>
+        <v>13</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>13</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>13</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>102</v>
+        <v>13</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>105</v>
+        <v>13</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>112</v>
+        <v>13</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>115</v>
+        <v>13</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>118</v>
+        <v>13</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>120</v>
+        <v>13</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>123</v>
+        <v>13</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>125</v>
+        <v>13</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>127</v>
+        <v>89</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>128</v>
+        <v>84</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>131</v>
+        <v>13</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>135</v>
+        <v>101</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>137</v>
+        <v>13</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>139</v>
+        <v>13</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>141</v>
+        <v>13</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>143</v>
+      <c r="G64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>146</v>
+        <v>13</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I66" s="1"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>149</v>
+        <v>13</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>151</v>
+        <v>13</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>153</v>
+        <v>13</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>155</v>
+        <v>142</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>158</v>
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>159</v>
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>162</v>
+        <v>142</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>164</v>
+        <v>13</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="76">
@@ -2307,19 +2761,25 @@
         <v>165</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>167</v>
+        <v>13</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -2327,119 +2787,51 @@
         <v>165</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>66</v>
+        <v>173</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>168</v>
+        <v>13</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/diccionarioDatosDelivery.xlsx
+++ b/diccionarioDatosDelivery.xlsx
@@ -55,7 +55,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Identificador único autoincremental de la suscripción [cite: 57].</t>
+    <t>Identificador único autoincremental de la suscripción.</t>
   </si>
   <si>
     <t>tipo</t>
@@ -64,7 +64,7 @@
     <t>VARCHAR(50)</t>
   </si>
   <si>
-    <t>Nombre o categoría del plan (ej. Premium) [cite: 57].</t>
+    <t>Nombre o categoría del plan (ej. Premium).</t>
   </si>
   <si>
     <t>costo_mensual</t>
@@ -73,7 +73,7 @@
     <t>DECIMAL(10,2)</t>
   </si>
   <si>
-    <t>Precio mensual de la suscripción [cite: 57].</t>
+    <t>Precio mensual de la suscripción.</t>
   </si>
   <si>
     <t>descuento_envio</t>
@@ -82,7 +82,7 @@
     <t>DECIMAL(5,2)</t>
   </si>
   <si>
-    <t>Porcentaje de descuento aplicado a los envíos [cite: 57].</t>
+    <t>Porcentaje de descuento aplicado a los envíos.</t>
   </si>
   <si>
     <t>REPARTIDOR</t>
@@ -91,7 +91,7 @@
     <t>id_repartidor</t>
   </si>
   <si>
-    <t>Identificador único del repartidor [cite: 65].</t>
+    <t>Identificador único del repartidor.</t>
   </si>
   <si>
     <t>nombre</t>
@@ -100,13 +100,13 @@
     <t>VARCHAR(100)</t>
   </si>
   <si>
-    <t>Nombre completo del repartidor [cite: 65].</t>
+    <t>Nombre completo del repartidor.</t>
   </si>
   <si>
     <t>vehiculo</t>
   </si>
   <si>
-    <t>Tipo de transporte (bicicleta, moto, auto) [cite:20, 65]</t>
+    <t>Tipo de transporte (bicicleta, moto, auto).</t>
   </si>
   <si>
     <t>telefono</t>
@@ -115,7 +115,7 @@
     <t>VARCHAR(20)</t>
   </si>
   <si>
-    <t>Número de contacto del repartidor [cite: 65].</t>
+    <t>Número de contacto del repartidor.</t>
   </si>
   <si>
     <t>calificacion_promedio</t>
@@ -124,7 +124,7 @@
     <t>DECIMAL(3,2)</t>
   </si>
   <si>
-    <t>Promedio de notas recibidas por clientes [cite: 65].</t>
+    <t>Promedio de notas recibidas por clientes.</t>
   </si>
   <si>
     <t>CUPON</t>
@@ -133,19 +133,19 @@
     <t>id_cupon</t>
   </si>
   <si>
-    <t>Identificador único del cupón [cite: 66].</t>
+    <t>Identificador único del cupón.</t>
   </si>
   <si>
     <t>codigo</t>
   </si>
   <si>
-    <t>Código alfanumérico único para aplicar el descuento [cite: 66].</t>
+    <t>Código alfanumérico único para aplicar el descuento.</t>
   </si>
   <si>
     <t>porcentaje</t>
   </si>
   <si>
-    <t>Porcentaje de rebaja sobre el pedido [cite: 66].</t>
+    <t>Porcentaje de rebaja sobre el pedido.</t>
   </si>
   <si>
     <t>fecha_expira</t>
@@ -154,13 +154,13 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>Fecha límite de validez del cupón [cite: 66].</t>
+    <t>Fecha límite de validez del cupón.</t>
   </si>
   <si>
     <t>estado</t>
   </si>
   <si>
-    <t>Estado actual del cupón (ej. Activo/Inactivo) [cite: 66].</t>
+    <t>Estado actual del cupón (ej. Activo/Inactivo).</t>
   </si>
   <si>
     <t>COMERCIO</t>
@@ -169,16 +169,16 @@
     <t>id_comercio</t>
   </si>
   <si>
-    <t>Identificador único del comercio [cite: 60].</t>
-  </si>
-  <si>
-    <t>Nombre del establecimiento comercial [cite: 60].</t>
+    <t>Identificador único del comercio.</t>
+  </si>
+  <si>
+    <t>Nombre del establecimiento comercial.</t>
   </si>
   <si>
     <t>rubro</t>
   </si>
   <si>
-    <t>Categoría del negocio (ej. Comida Rápida) [cite: 60].</t>
+    <t>Categoría del negocio (ej. Comida Rápida).</t>
   </si>
   <si>
     <t>direccion</t>
@@ -187,7 +187,7 @@
     <t>VARCHAR(200)</t>
   </si>
   <si>
-    <t>Dirección física del comercio [cite: 60].</t>
+    <t>Dirección física del comercio.</t>
   </si>
   <si>
     <t>latitud</t>
@@ -196,7 +196,7 @@
     <t>DECIMAL(10,8)</t>
   </si>
   <si>
-    <t>Coordenada de latitud para GPS [cite: 60].</t>
+    <t>Coordenada de latitud para GPS.</t>
   </si>
   <si>
     <t>longitud</t>
@@ -205,7 +205,7 @@
     <t>DECIMAL(11,8)</t>
   </si>
   <si>
-    <t>Coordenada de longitud para GPS [cite: 60].</t>
+    <t>Coordenada de longitud para GPS.</t>
   </si>
   <si>
     <t>CLIENTE</t>
@@ -214,19 +214,19 @@
     <t>id_cliente</t>
   </si>
   <si>
-    <t>Identificador único del cliente [cite: 58].</t>
-  </si>
-  <si>
-    <t>Nombre completo del usuario [cite: 58].</t>
+    <t>Identificador único del cliente.</t>
+  </si>
+  <si>
+    <t>Nombre completo del usuario.</t>
   </si>
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>Correo electrónico único de registro [cite: 58].</t>
-  </si>
-  <si>
-    <t>Teléfono de contacto del cliente [cite: 58].</t>
+    <t>Correo electrónico único de registro.</t>
+  </si>
+  <si>
+    <t>Teléfono de contacto del cliente.</t>
   </si>
   <si>
     <t>INT</t>
@@ -235,7 +235,7 @@
     <t>SUSCRIPCION(id_suscripcion)</t>
   </si>
   <si>
-    <t>Referencia al plan de suscripción contratado [cite: 58].</t>
+    <t>Referencia al plan de suscripción contratado.</t>
   </si>
   <si>
     <t>PRODUCTO</t>
@@ -244,10 +244,10 @@
     <t>id_producto</t>
   </si>
   <si>
-    <t>Identificador único del producto [cite: 61].</t>
-  </si>
-  <si>
-    <t>Nombre comercial del producto [cite: 61].</t>
+    <t>Identificador único del producto.</t>
+  </si>
+  <si>
+    <t>Nombre comercial del producto.</t>
   </si>
   <si>
     <t>descripcion</t>
@@ -256,19 +256,19 @@
     <t>TEXT</t>
   </si>
   <si>
-    <t>Detalle o ingredientes del producto [cite: 61].</t>
+    <t>Detalle o ingredientes del producto.</t>
   </si>
   <si>
     <t>precio</t>
   </si>
   <si>
-    <t>Valor unitario del producto [cite: 61].</t>
+    <t>Valor unitario del producto.</t>
   </si>
   <si>
     <t>COMERCIO(id_comercio)</t>
   </si>
   <si>
-    <t>Referencia al comercio que ofrece el producto [cite: 61].</t>
+    <t>Referencia al comercio que ofrece el producto.</t>
   </si>
   <si>
     <t>DIRECCION</t>
@@ -277,13 +277,13 @@
     <t>id_direccion</t>
   </si>
   <si>
-    <t>Identificador único de la dirección [cite: 59].</t>
+    <t>Identificador único de la dirección.</t>
   </si>
   <si>
     <t>CLIENTE(id_cliente)</t>
   </si>
   <si>
-    <t>Referencia al cliente dueño de la dirección [cite: 59].</t>
+    <t>Referencia al cliente dueño de la dirección.</t>
   </si>
   <si>
     <t>calle</t>
@@ -292,19 +292,19 @@
     <t>VARCHAR(150)</t>
   </si>
   <si>
-    <t>Nombre de la vía o calle [cite: 59].</t>
+    <t>Nombre de la vía o calle.</t>
   </si>
   <si>
     <t>numero</t>
   </si>
   <si>
-    <t>Numeración domiciliaria [cite: 59].</t>
-  </si>
-  <si>
-    <t>Ubicación geográfica (latitud) [cite: 59].</t>
-  </si>
-  <si>
-    <t>Ubicación geográfica (longitud) [cite: 59].</t>
+    <t>Numeración domiciliaria.</t>
+  </si>
+  <si>
+    <t>Ubicación geográfica (latitud).</t>
+  </si>
+  <si>
+    <t>Ubicación geográfica (longitud).</t>
   </si>
   <si>
     <t>COMPLEMENTO</t>
@@ -313,22 +313,22 @@
     <t>id_complemento</t>
   </si>
   <si>
-    <t>ID único del complemento o extra [cite: 62].</t>
+    <t>ID único del complemento o extra.</t>
   </si>
   <si>
     <t>PRODUCTO(id_producto)</t>
   </si>
   <si>
-    <t>Referencia al producto al que se asocia [cite: 62].</t>
-  </si>
-  <si>
-    <t>Nombre del extra (ej. Queso extra) [cite: 62].</t>
+    <t>Referencia al producto al que se asocia.</t>
+  </si>
+  <si>
+    <t>Nombre del extra (ej. Queso extra).</t>
   </si>
   <si>
     <t>precio_extra</t>
   </si>
   <si>
-    <t>Costo adicional por el complemento [cite: 62].</t>
+    <t>Costo adicional por el complemento.</t>
   </si>
   <si>
     <t>CARRITO</t>
@@ -337,10 +337,10 @@
     <t>id_carrito</t>
   </si>
   <si>
-    <t>Identificador del carrito de compra [cite: 63].</t>
-  </si>
-  <si>
-    <t>Referencia al cliente propietario del carrito [cite: 63].</t>
+    <t>Identificador del carrito de compra.</t>
+  </si>
+  <si>
+    <t>Referencia al cliente propietario del carrito.</t>
   </si>
   <si>
     <t>fecha_creacion</t>
@@ -349,7 +349,7 @@
     <t>TIMESTAMP</t>
   </si>
   <si>
-    <t>Fecha y hora de inicio de la sesión de compra [cite: 63].</t>
+    <t>Fecha y hora de inicio de la sesión de compra.</t>
   </si>
   <si>
     <t>ITEM_CARRITO</t>
@@ -358,22 +358,22 @@
     <t>id_item</t>
   </si>
   <si>
-    <t>ID de la línea de producto en el carrito [cite: 64].</t>
+    <t>ID de la línea de producto en el carrito.</t>
   </si>
   <si>
     <t>CARRITO(id_carrito)</t>
   </si>
   <si>
-    <t>Referencia al carrito principal [cite: 64].</t>
-  </si>
-  <si>
-    <t>Referencia al producto seleccionado [cite: 64].</t>
+    <t>Referencia al carrito principal.</t>
+  </si>
+  <si>
+    <t>Referencia al producto seleccionado.</t>
   </si>
   <si>
     <t>cantidad</t>
   </si>
   <si>
-    <t>Unidades del producto en el carrito [cite: 64].</t>
+    <t>Unidades del producto en el carrito.</t>
   </si>
   <si>
     <t>PEDIDO</t>
@@ -382,25 +382,25 @@
     <t>id_pedido</t>
   </si>
   <si>
-    <t>Identificador único del pedido finalizado [cite: 67].</t>
+    <t>Identificador único del pedido finalizado.</t>
   </si>
   <si>
     <t>fecha</t>
   </si>
   <si>
-    <t>Fecha y hora de generación del pedido [cite: 67].</t>
+    <t>Fecha y hora de generación del pedido.</t>
   </si>
   <si>
     <t>total_productos</t>
   </si>
   <si>
-    <t>Suma total de precios de productos [cite: 67].</t>
+    <t>Suma total de precios de productos.</t>
   </si>
   <si>
     <t>costo_envio</t>
   </si>
   <si>
-    <t>Cargo por transporte y logística [cite: 39, 67]</t>
+    <t>Cargo por transporte y logística.</t>
   </si>
   <si>
     <t>distancia_km</t>
@@ -409,25 +409,25 @@
     <t>DECIMAL(6,2)</t>
   </si>
   <si>
-    <t>Distancia recorrida para la entrega [cite: 67].</t>
-  </si>
-  <si>
-    <t>Cliente que realiza la compra [cite: 67].</t>
-  </si>
-  <si>
-    <t>Comercio donde se realiza la compra [cite: 67].</t>
+    <t>Distancia recorrida para la entrega.</t>
+  </si>
+  <si>
+    <t>Cliente que realiza la compra.</t>
+  </si>
+  <si>
+    <t>Comercio donde se realiza la compra.</t>
   </si>
   <si>
     <t>REPARTIDOR(id_repartidor)</t>
   </si>
   <si>
-    <t>Repartidor asignado al traslado [cite: 67].</t>
+    <t>Repartidor asignado al traslado.</t>
   </si>
   <si>
     <t>CUPON(id_cupon)</t>
   </si>
   <si>
-    <t>Cupón de descuento aplicado [cite: 67].</t>
+    <t>Cupón de descuento aplicado.</t>
   </si>
   <si>
     <t>DETALLE_PEDIDO</t>
@@ -463,31 +463,31 @@
     <t>id_pago</t>
   </si>
   <si>
-    <t>Identificador único de la transacción [cite: 68].</t>
-  </si>
-  <si>
-    <t>Referencia al pedido pagado [cite: 68].</t>
+    <t>Identificador único de la transacción.</t>
+  </si>
+  <si>
+    <t>Referencia al pedido pagado.</t>
   </si>
   <si>
     <t>metodo_pago</t>
   </si>
   <si>
-    <t>Medio de pago utilizado (ej. Débito) [cite: 68].</t>
+    <t>Medio de pago utilizado (ej. Débito).</t>
   </si>
   <si>
     <t>monto_final</t>
   </si>
   <si>
-    <t>Total pagado tras descuentos [cite: 68].</t>
-  </si>
-  <si>
-    <t>Estado de la transacción (ej. Aprobado) [cite: 68].</t>
+    <t>Total pagado tras descuentos.</t>
+  </si>
+  <si>
+    <t>Estado de la transacción (ej. Aprobado).</t>
   </si>
   <si>
     <t>fecha_pago</t>
   </si>
   <si>
-    <t>Fecha y hora de confirmación del pago [cite: 68].</t>
+    <t>Fecha y hora de confirmación del pago.</t>
   </si>
   <si>
     <t>RECLAMO</t>
@@ -514,34 +514,34 @@
     <t>id_valoracion</t>
   </si>
   <si>
-    <t>Identificador único de la calificación [cite: 70].</t>
-  </si>
-  <si>
-    <t>Referencia al pedido evaluado [cite: 70].</t>
+    <t>Identificador único de la calificación.</t>
+  </si>
+  <si>
+    <t>Referencia al pedido evaluado.</t>
   </si>
   <si>
     <t>nota_comercio</t>
   </si>
   <si>
-    <t>Calificación al local (1-5) [cite: 60, 70]</t>
+    <t>Calificación al local (1-5).</t>
   </si>
   <si>
     <t>nota_repartidor</t>
   </si>
   <si>
-    <t>Calificación al repartidor (1-5) [cite: 60, 70]</t>
+    <t>Calificación al repartidor (1-5).</t>
   </si>
   <si>
     <t>comentario</t>
   </si>
   <si>
-    <t>Opinión escrita del cliente [cite: 70].</t>
+    <t>Opinión escrita del cliente.</t>
   </si>
   <si>
     <t>fecha_valoracion</t>
   </si>
   <si>
-    <t>Fecha de registro de la reseña [cite: 70].</t>
+    <t>Fecha de registro de la reseña.</t>
   </si>
 </sst>
 </file>
